--- a/backend/wp_templates/L/L4 应付债券.xlsx
+++ b/backend/wp_templates/L/L4 应付债券.xlsx
@@ -24514,11 +24514,11 @@
       <c r="P13" s="230"/>
       <c r="Q13" s="230"/>
       <c r="R13" s="58">
-        <f t="shared" ref="R13:S18" si="0">L13+N13-P13</f>
+        <f>L13+N13-P13</f>
         <v>0</v>
       </c>
       <c r="S13" s="58">
-        <f t="shared" si="0"/>
+        <f>M13+O13-Q13</f>
         <v>0</v>
       </c>
       <c r="T13" s="237"/>
@@ -24534,35 +24534,35 @@
       <c r="AD13" s="230"/>
       <c r="AE13" s="230"/>
       <c r="AF13" s="58">
-        <f t="shared" ref="AF13:AG17" si="1">L13+T13+V13</f>
+        <f>L13+T13+V13</f>
         <v>0</v>
       </c>
       <c r="AG13" s="58">
-        <f t="shared" si="1"/>
+        <f>M13+U13+W13</f>
         <v>0</v>
       </c>
       <c r="AH13" s="58">
-        <f t="shared" ref="AH13:AK17" si="2">N13+X13+AB13</f>
+        <f>N13+X13+AB13</f>
         <v>0</v>
       </c>
       <c r="AI13" s="58">
-        <f t="shared" si="2"/>
+        <f>O13+Y13+AC13</f>
         <v>0</v>
       </c>
       <c r="AJ13" s="58">
-        <f t="shared" si="2"/>
+        <f>P13+Z13+AD13</f>
         <v>0</v>
       </c>
       <c r="AK13" s="58">
-        <f t="shared" si="2"/>
+        <f>Q13+AA13+AE13</f>
         <v>0</v>
       </c>
       <c r="AL13" s="58">
-        <f t="shared" ref="AL13:AM18" si="3">AF13+AH13-AJ13</f>
+        <f>AF13+AH13-AJ13</f>
         <v>0</v>
       </c>
       <c r="AM13" s="58">
-        <f t="shared" si="3"/>
+        <f>AG13+AI13-AK13</f>
         <v>0</v>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
       <c r="P14" s="230"/>
       <c r="Q14" s="230"/>
       <c r="R14" s="58">
-        <f t="shared" si="0"/>
+        <f>L14+N14-P14</f>
         <v>0</v>
       </c>
       <c r="S14" s="58">
-        <f t="shared" si="0"/>
+        <f>M14+O14-Q14</f>
         <v>0</v>
       </c>
       <c r="T14" s="237"/>
@@ -24605,35 +24605,35 @@
       <c r="AD14" s="230"/>
       <c r="AE14" s="230"/>
       <c r="AF14" s="58">
-        <f t="shared" si="1"/>
+        <f>L14+T14+V14</f>
         <v>0</v>
       </c>
       <c r="AG14" s="58">
-        <f t="shared" si="1"/>
+        <f>M14+U14+W14</f>
         <v>0</v>
       </c>
       <c r="AH14" s="58">
-        <f t="shared" si="2"/>
+        <f>N14+X14+AB14</f>
         <v>0</v>
       </c>
       <c r="AI14" s="58">
-        <f t="shared" si="2"/>
+        <f>O14+Y14+AC14</f>
         <v>0</v>
       </c>
       <c r="AJ14" s="58">
-        <f t="shared" si="2"/>
+        <f>P14+Z14+AD14</f>
         <v>0</v>
       </c>
       <c r="AK14" s="58">
-        <f t="shared" si="2"/>
+        <f>Q14+AA14+AE14</f>
         <v>0</v>
       </c>
       <c r="AL14" s="58">
-        <f t="shared" si="3"/>
+        <f>AF14+AH14-AJ14</f>
         <v>0</v>
       </c>
       <c r="AM14" s="58">
-        <f t="shared" si="3"/>
+        <f>AG14+AI14-AK14</f>
         <v>0</v>
       </c>
     </row>
@@ -24656,11 +24656,11 @@
       <c r="P15" s="230"/>
       <c r="Q15" s="230"/>
       <c r="R15" s="58">
-        <f t="shared" si="0"/>
+        <f>L15+N15-P15</f>
         <v>0</v>
       </c>
       <c r="S15" s="58">
-        <f t="shared" si="0"/>
+        <f>M15+O15-Q15</f>
         <v>0</v>
       </c>
       <c r="T15" s="237"/>
@@ -24676,35 +24676,35 @@
       <c r="AD15" s="230"/>
       <c r="AE15" s="230"/>
       <c r="AF15" s="58">
-        <f t="shared" si="1"/>
+        <f>L15+T15+V15</f>
         <v>0</v>
       </c>
       <c r="AG15" s="58">
-        <f t="shared" si="1"/>
+        <f>M15+U15+W15</f>
         <v>0</v>
       </c>
       <c r="AH15" s="58">
-        <f t="shared" si="2"/>
+        <f>N15+X15+AB15</f>
         <v>0</v>
       </c>
       <c r="AI15" s="58">
-        <f t="shared" si="2"/>
+        <f>O15+Y15+AC15</f>
         <v>0</v>
       </c>
       <c r="AJ15" s="58">
-        <f t="shared" si="2"/>
+        <f>P15+Z15+AD15</f>
         <v>0</v>
       </c>
       <c r="AK15" s="58">
-        <f t="shared" si="2"/>
+        <f>Q15+AA15+AE15</f>
         <v>0</v>
       </c>
       <c r="AL15" s="58">
-        <f t="shared" si="3"/>
+        <f>AF15+AH15-AJ15</f>
         <v>0</v>
       </c>
       <c r="AM15" s="58">
-        <f t="shared" si="3"/>
+        <f>AG15+AI15-AK15</f>
         <v>0</v>
       </c>
     </row>
@@ -24727,11 +24727,11 @@
       <c r="P16" s="230"/>
       <c r="Q16" s="230"/>
       <c r="R16" s="58">
-        <f t="shared" si="0"/>
+        <f>L16+N16-P16</f>
         <v>0</v>
       </c>
       <c r="S16" s="58">
-        <f t="shared" si="0"/>
+        <f>M16+O16-Q16</f>
         <v>0</v>
       </c>
       <c r="T16" s="237"/>
@@ -24747,35 +24747,35 @@
       <c r="AD16" s="230"/>
       <c r="AE16" s="230"/>
       <c r="AF16" s="58">
-        <f t="shared" si="1"/>
+        <f>L16+T16+V16</f>
         <v>0</v>
       </c>
       <c r="AG16" s="58">
-        <f t="shared" si="1"/>
+        <f>M16+U16+W16</f>
         <v>0</v>
       </c>
       <c r="AH16" s="58">
-        <f t="shared" si="2"/>
+        <f>N16+X16+AB16</f>
         <v>0</v>
       </c>
       <c r="AI16" s="58">
-        <f t="shared" si="2"/>
+        <f>O16+Y16+AC16</f>
         <v>0</v>
       </c>
       <c r="AJ16" s="58">
-        <f t="shared" si="2"/>
+        <f>P16+Z16+AD16</f>
         <v>0</v>
       </c>
       <c r="AK16" s="58">
-        <f t="shared" si="2"/>
+        <f>Q16+AA16+AE16</f>
         <v>0</v>
       </c>
       <c r="AL16" s="58">
-        <f t="shared" si="3"/>
+        <f>AF16+AH16-AJ16</f>
         <v>0</v>
       </c>
       <c r="AM16" s="58">
-        <f t="shared" si="3"/>
+        <f>AG16+AI16-AK16</f>
         <v>0</v>
       </c>
     </row>
@@ -24798,11 +24798,11 @@
       <c r="P17" s="230"/>
       <c r="Q17" s="230"/>
       <c r="R17" s="58">
-        <f t="shared" si="0"/>
+        <f>L17+N17-P17</f>
         <v>0</v>
       </c>
       <c r="S17" s="58">
-        <f t="shared" si="0"/>
+        <f>M17+O17-Q17</f>
         <v>0</v>
       </c>
       <c r="T17" s="237"/>
@@ -24818,35 +24818,35 @@
       <c r="AD17" s="230"/>
       <c r="AE17" s="230"/>
       <c r="AF17" s="58">
-        <f t="shared" si="1"/>
+        <f>L17+T17+V17</f>
         <v>0</v>
       </c>
       <c r="AG17" s="58">
-        <f t="shared" si="1"/>
+        <f>M17+U17+W17</f>
         <v>0</v>
       </c>
       <c r="AH17" s="58">
-        <f t="shared" si="2"/>
+        <f>N17+X17+AB17</f>
         <v>0</v>
       </c>
       <c r="AI17" s="58">
-        <f t="shared" si="2"/>
+        <f>O17+Y17+AC17</f>
         <v>0</v>
       </c>
       <c r="AJ17" s="58">
-        <f t="shared" si="2"/>
+        <f>P17+Z17+AD17</f>
         <v>0</v>
       </c>
       <c r="AK17" s="58">
-        <f t="shared" si="2"/>
+        <f>Q17+AA17+AE17</f>
         <v>0</v>
       </c>
       <c r="AL17" s="58">
-        <f t="shared" si="3"/>
+        <f>AF17+AH17-AJ17</f>
         <v>0</v>
       </c>
       <c r="AM17" s="58">
-        <f t="shared" si="3"/>
+        <f>AG17+AI17-AK17</f>
         <v>0</v>
       </c>
     </row>
@@ -24865,35 +24865,35 @@
       <c r="J18" s="58"/>
       <c r="K18" s="58"/>
       <c r="L18" s="58">
-        <f t="shared" ref="L18:Q18" si="4">SUM(L13:L17)</f>
+        <f>SUM(L13:L17)</f>
         <v>0</v>
       </c>
       <c r="M18" s="58">
-        <f t="shared" si="4"/>
+        <f>SUM(M13:M17)</f>
         <v>0</v>
       </c>
       <c r="N18" s="58">
-        <f t="shared" si="4"/>
+        <f>SUM(N13:N17)</f>
         <v>0</v>
       </c>
       <c r="O18" s="58">
-        <f t="shared" si="4"/>
+        <f>SUM(O13:O17)</f>
         <v>0</v>
       </c>
       <c r="P18" s="58">
-        <f t="shared" si="4"/>
+        <f>SUM(P13:P17)</f>
         <v>0</v>
       </c>
       <c r="Q18" s="58">
-        <f t="shared" si="4"/>
+        <f>SUM(Q13:Q17)</f>
         <v>0</v>
       </c>
       <c r="R18" s="58">
-        <f t="shared" si="0"/>
+        <f>L18+N18-P18</f>
         <v>0</v>
       </c>
       <c r="S18" s="58">
-        <f t="shared" si="0"/>
+        <f>M18+O18-Q18</f>
         <v>0</v>
       </c>
       <c r="T18" s="58">
@@ -24913,67 +24913,67 @@
         <v>0</v>
       </c>
       <c r="X18" s="58">
-        <f t="shared" ref="X18:AK18" si="5">SUM(X13:X17)</f>
+        <f>SUM(X13:X17)</f>
         <v>0</v>
       </c>
       <c r="Y18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(Y13:Y17)</f>
         <v>0</v>
       </c>
       <c r="Z18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(Z13:Z17)</f>
         <v>0</v>
       </c>
       <c r="AA18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AA13:AA17)</f>
         <v>0</v>
       </c>
       <c r="AB18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AB13:AB17)</f>
         <v>0</v>
       </c>
       <c r="AC18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AC13:AC17)</f>
         <v>0</v>
       </c>
       <c r="AD18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AD13:AD17)</f>
         <v>0</v>
       </c>
       <c r="AE18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AE13:AE17)</f>
         <v>0</v>
       </c>
       <c r="AF18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AF13:AF17)</f>
         <v>0</v>
       </c>
       <c r="AG18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AG13:AG17)</f>
         <v>0</v>
       </c>
       <c r="AH18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AH13:AH17)</f>
         <v>0</v>
       </c>
       <c r="AI18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AI13:AI17)</f>
         <v>0</v>
       </c>
       <c r="AJ18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AJ13:AJ17)</f>
         <v>0</v>
       </c>
       <c r="AK18" s="58">
-        <f t="shared" si="5"/>
+        <f>SUM(AK13:AK17)</f>
         <v>0</v>
       </c>
       <c r="AL18" s="58">
-        <f t="shared" si="3"/>
+        <f>AF18+AH18-AJ18</f>
         <v>0</v>
       </c>
       <c r="AM18" s="58">
-        <f t="shared" si="3"/>
+        <f>AG18+AI18-AK18</f>
         <v>0</v>
       </c>
     </row>
@@ -26241,7 +26241,6 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D61" r:id="rId1"/>
     <hyperlink ref="N3" location="底稿目录!A1" display="=底稿目录!F10"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>

--- a/backend/wp_templates/L/L4 应付债券.xlsx
+++ b/backend/wp_templates/L/L4 应付债券.xlsx
@@ -18759,7 +18759,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="300">
-        <f>'应付债券明细表L4-2'!I17</f>
+        <f>'应付债券明细表L4-2'!I19</f>
         <v>0</v>
       </c>
     </row>
@@ -18793,7 +18793,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="300">
-        <f>'应付债券明细表L4-2'!I18</f>
+        <f>'应付债券明细表L4-2'!I20</f>
         <v>0</v>
       </c>
     </row>
@@ -24897,19 +24897,19 @@
         <v>0</v>
       </c>
       <c r="T18" s="58">
-        <f>N18+P18-R18</f>
+        <f>SUM(T13:T17)</f>
         <v>0</v>
       </c>
       <c r="U18" s="58">
-        <f>O18+Q18-S18</f>
+        <f>SUM(U13:U17)</f>
         <v>0</v>
       </c>
       <c r="V18" s="58">
-        <f>P18+R18-T18</f>
+        <f>SUM(V13:V17)</f>
         <v>0</v>
       </c>
       <c r="W18" s="58">
-        <f>Q18+S18-U18</f>
+        <f>SUM(W13:W17)</f>
         <v>0</v>
       </c>
       <c r="X18" s="58">
